--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923FC22A-8FCD-4028-A5D8-6829C420B52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1AD972-0B88-4807-A687-77DD9905D2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="133">
   <si>
     <t>Nome do produto</t>
   </si>
@@ -419,6 +419,9 @@
   </si>
   <si>
     <t>Não renomeie a aba 'Produtos' nem as colunas — o site lê por esses nomes.</t>
+  </si>
+  <si>
+    <t>TESTE</t>
   </si>
 </sst>
 </file>
@@ -561,8 +564,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -572,6 +573,8 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1507,12 +1510,24 @@
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="7"/>
+      <c r="A29" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="7">
+        <v>10</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="7">
+        <v>4</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
@@ -5261,7 +5276,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5848,13 +5864,13 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="18">
+      <c r="A54" s="16">
         <v>46143</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="18">
         <v>1.07</v>
       </c>
-      <c r="C54" s="19">
+      <c r="C54" s="17">
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -5958,10 +5974,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
